--- a/artfynd/A 14947-2023 artfynd.xlsx
+++ b/artfynd/A 14947-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14947-2023 artfynd.xlsx
+++ b/artfynd/A 14947-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68659424</v>
+        <v>68659415</v>
       </c>
       <c r="B2" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428503.8468942093</v>
+        <v>428389</v>
       </c>
       <c r="R2" t="n">
-        <v>6502385.917922098</v>
+        <v>6502427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68659415</v>
+        <v>68659421</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428388.860990699</v>
+        <v>428465</v>
       </c>
       <c r="R3" t="n">
-        <v>6502427.062942802</v>
+        <v>6502388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2016-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>68659423</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428492.9019350482</v>
+        <v>428493</v>
       </c>
       <c r="R4" t="n">
-        <v>6502386.119000362</v>
+        <v>6502386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +946,9 @@
           <t>2016-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68659421</v>
+        <v>68659425</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,17 +1003,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>E20 Mariestad - Götene, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428464.786442637</v>
+        <v>428501</v>
       </c>
       <c r="R5" t="n">
-        <v>6502388.196919101</v>
+        <v>6502387</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1052,9 @@
           <t>2016-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,59 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68659425</v>
+        <v>68659424</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>E20 Mariestad - Götene, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428501.2600662034</v>
+        <v>428504</v>
       </c>
       <c r="R6" t="n">
-        <v>6502387.006274589</v>
+        <v>6502386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,19 +1149,9 @@
           <t>2016-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14947-2023 artfynd.xlsx
+++ b/artfynd/A 14947-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68659415</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68659421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68659423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68659425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,8 +1200,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68659424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>